--- a/output/citadele_reviews_latest.xlsx
+++ b/output/citadele_reviews_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Reviews'!$A$1:$K$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Reviews'!$A$1:$K$148</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3021,8 +3021,5325 @@
         <v>1</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Parslegsana starp kontiem</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Jau nedēļu aplikācija nestrādā ! Ne no datora nevar Ienākt konta ne no telefona. Lai dabūt piekļuvi vaj dokumentus jascane, va dzēst un lejupielādēt no jauna.</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Cienījamais</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>46.4</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30T06:27:45-07:00</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>14245121606</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1939142419</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Lagging</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Lagging all the time</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Sandro P S</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>46.1</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10T05:49:08-07:00</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>14165924083</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id991825809</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Requires canera access</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Requires camera access for face scan despite the customer has other authentication tools.</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Oblivious Reawake</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>46.1</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10T01:16:20-07:00</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>14165218601</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1931282409</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Зависает</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Периодически зависает на от какой нибудь страничке приложения. Не понятно как перезапустить. А когда нужно что-то срочно сделать, оплатить это очень мешает.</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Irinaromance</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>46.1</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29T02:05:01-07:00</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>14118721418</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1774791733</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Password</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Very laggy, i cant make new password</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Hahakdkakw</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>46.1</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12T03:07:56-07:00</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>14055672060</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1015219998</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Best</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Best of the Best</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>AnnaJe</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>46.1</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10T09:58:21-07:00</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>14049672987</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id374669959</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Titulis</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Lūdzu, izlabojiet, lai versija priekš iOS16 (iphone8) var lietot Atlikums funkciju..
+Šobrīd vairs tālāk par login logu nevar tikt..
+(iPhone 8/X vēl saņem security updates, bet nevar uz iOS 17 upgradot)</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>NeviensNekurNekad</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25T17:35:06-07:00</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>13997219931</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1182576565</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Maksājums</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Ātri un ērti</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Nordstock</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>46.0</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-21T00:09:34-07:00</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>13980784641</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id474740478</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Zero support and feedback</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Problem with login, this app already more than half year has  issue with login, it doesn't remember your login and need everytime fill name, it isn't matter chosed you "remember login" or not. And everytime after login it shows "Error. Something gone wrong." I reported about problem to support but they didn't fixed or normally replied, but asked my passport data. Also this app has a lot of cutted off possibilities if compare with internet bank web page, that cause stupid situation then need app to login in web page to change something. At one device I need two different logins to do one simple thing.</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Emelint</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>46.0</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14T22:20:50-07:00</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>13959369731</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1175503973</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Good ap</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>BMX boy673</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>46.0</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-03T03:53:43-07:00</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>13917409833</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1907543400</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Izrādās lai piekłūtu kontam ir nepieciešams jaunākās versijas IOS, pārējiem banka telefonā slēgta</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Łoti negorši no CITADELE puses nobloket iespēju ieiet internet bankas aplikacija tikai tāpēc, ka nepatīk programmaturas versija, galīgi nav forši kā klientam pēkšñi attapties, ka pieeja bankai ir ietobežota tikai tāpēc ka nepatīk IOS versija, neko šādu no bankas gan negaidīju !</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Nonnn. N</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-02T05:59:32-07:00</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>13704714125</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1344867938</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Pro Bank</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>The bank is friendly, the staff are very helpful, and they assisted me a lot when I needed help.</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Chuyên nghiệp Bank</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>45.7</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-22T23:54:22-07:00</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>13665503813</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1614644439</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Forša aplikācija</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Lieliska aplikācija, strādā bez problèmām, var piekłūt ar pirkta nospieduma un saņemt notifikācijas par maksājumiem, citām bankām šādas opcijas nevienmēr ir</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Ine098</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>45.7</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-15T02:19:42-07:00</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>13635607369</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id601426458</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Reklāmas aplikācija</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Tas ir noragašanas par lietotāju likt sadaļu kur Tev tamborē par “aktualitātēm” t.i. REKLĀMA!!! Pārejas sadaļas var mainīt vietām, bet šo nē. 110% besis par to!</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>ivasap</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>45.7</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-26T11:39:18-07:00</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>13558125017</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id338039968</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Forced updates</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Aplikācija vairs nestrādā jo man jāpērk jauns telefons, tā vismaz Citadele banka uzskata :)</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Helmuts no tatarstānas</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-01T01:10:43-07:00</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>13461819713</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id555983244</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Stopped working on my Iphone X ios16. Thats bad service.</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Should work as long as I have this phone where app was installed. Bank wants me to buy a new phone. Now I got a new trouble to solve. Mau be time ti change bank?</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Janis Alnis</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-11T04:10:17-07:00</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>13252100973</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1040374104</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Favorite bank app</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Very nice banking app and simple to use too. My father has been using it for years, I was only about 11 or 12 years old when he got me my first Citadele credit card:) Since then also my mom started using this app and then my brother, seems like such a simple thing but it makes the transactions so much easier between us. We also really love Citadele rewards, recently I bought a delicious drink using my points, it was deffinetly worth it!😊</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>CarryMilka</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-08T05:48:31-07:00</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>13239773092</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1564549114</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Ужасное обновление</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Постоянно глючит и выбрасывает с приложения!</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>IzabelleM0909</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-07T14:25:11-07:00</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>13237307199</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id376387269</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>VAZaharovs</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-30T00:54:50-07:00</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>13203622921</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1524302955</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>0,01 zvaigzne</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Sliktākā un nepārskatāmā internetbanka un aplikācija salīdzinājumā ar citām LV bankām</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Ainars-st</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-26T08:13:49-07:00</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>13187722367</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id302645165</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Built for the bank</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>A well-built for the bank app. Less things actually needed or usable for user, more options for the bank to advertise their services.</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>bor1s</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-21T23:53:12-07:00</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>12921454365</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id234315548</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Bad service</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Not recommend to use this bank. Trying to cheat with customers!</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Dennyuu</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>45.1</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-19T06:23:28-07:00</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>12673561062</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id634056739</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Отличная аппликация</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Всё нравится</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Инара123</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>45.1</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-15T12:29:11-07:00</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>12659844420</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1197238699</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>3D secure</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Don't display pop ap or never processing after confirm</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>yavoitkun</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-25T03:28:44-07:00</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>12583785194</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id245236028</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Mobile Scan</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Mobile scan isn't working as it did before. Now, when you need to enter your login number again and reach the section where you must input five digits, the mobile scan app doesn't let you in, displaying an incorrect PIN message. Only after refreshing the section does it approve your PIN. Poor service overall, and there is also no customer support available before 8:00 to provide direct assistance.</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Pāvils K</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-06T21:35:05-07:00</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>12513395456</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1625623163</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Jaunākā versija ļoti neērta</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Pēc pēdējā apdeita no ļoti patīkami intuitīvas, informatīvas un loģiski izkārtotas, aplikācija ir pārvērtusies par instagramu - liela, nekādu funkciju nepildoša bilde pa pusi ekrāna un visas noderīgās lietas sastumtas dziļi apakšlīmeņos. booo</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>mjhdhcdrgv</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>44.2</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-27T22:39:18-07:00</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>12239895359</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id424619615</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Don’t</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Dont upgrade. It is absolutely awful !!!</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>ggggedxcv</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>44.2</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-21T10:17:41-07:00</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>12089687475</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id484976580</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>My impressions of new software Citadele online</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>From banking systems and particularly online banking systems we, clients, do expect first of all stability, reliability and zero errors. I have been told (Dagnija Lacis from Unisys/Baltic Technology Group) that some North American banks are still using software, created with programming language “Cobold”. It was a long time ago, but operational system in ATM’s is still Windows XP, created in early 2000. So, conservative approach with most stable and familiar software is typical for serious banking. I was very satisfied with previous software version. And the second window with comments: open this and You’ll be surprised, seems a behaviour a little over fine red line of good banking behaviour. I do not expect some fun from my internet banking,  so I always skip that window unopened. And I don’t see any crucial improvements. 
+        Yours,
+                    Harry Jirgensons</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>harryjirgensons1</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-19T03:35:52-07:00</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>11967323448</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id899519474</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Bring the widget back 🥲</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>I like a new design, but I want to have the widget back (it disappeared after the update). I would also like to see the purchase statistics</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Hello world 228</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-09T01:24:34-07:00</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>11929502864</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id333444832</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Old version better</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Snezokllv</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-03T00:38:29-07:00</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>11906524124</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id309860745</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>New update</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>Ļoti slikti saprotama aplikācija. Nulle norādes/pamaciba, kur kas ir mainījies. 10min mekleju ka var stapr kontiem naudu parskaitīt. Lojalitātes punkti ari vairak nav redzami - tos vēl nēsmu atradis......</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>mamamamarks</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-31T11:18:07-07:00</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>11896721624</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id197646309</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>New version</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>Very bad. Everything that was on one screen is now hidden. And a bunch of unnecessary information that can't be removed.</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>MaxFyo</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-30T12:23:43-07:00</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>11893147382</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id686343029</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Jaunā versija ir briesmīga</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>Pusi ekrānu aizņem reklāmas un neko vairs nevar atrast</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Moriartijs</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-30T04:08:51-07:00</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>11891563650</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id303463227</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Jaunā versija</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>Pēc atjauninājuma nerādās widget ātrais atlikums. Pati aplikācija patīk un ir ērti lietojama. Ios versija 18.0.1</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>VirusStyle</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-29T10:05:35-07:00</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>11888892762</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id174655423</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>Jaunā versija</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>Jaunā versija ir kļuvusi sarežģītāka, mazāk patīkama. Vairāk laika un čakara pārslēgties no privātā uz biznesa kontu un apskatīt visus kontus. Tagad pārāk daudz mistiski piedāvājumi un reklàmas</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>andriskaposts</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-29T00:05:03-07:00</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>11887150057</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1381525443</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Наконец то!</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>Пользовался SEB еще неделю назад, все говорили что вы ахуенные. Не верил, потому что в Латвии такого быть не может. Все через одно место.  
+приятно удивлен! Эффект ВАУ получил от пользования вашего приложения. машины!!! Так держать 🫡🚀</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Terek89</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-27T01:56:02-07:00</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>11880100160</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id200358567</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Widgets</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>Pēc atjauninājuma pazuda widzets 😔</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Mar1sZ</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-26T08:42:52-07:00</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>11877476720</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id493922254</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>App update</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>Galīgi garām- galvenajā lapā tagad zem galvenā konta ir reklāma!  Pirms tam bija redzami visi konti. Tagad papildus jāpiespiež VISI konti, lai redzētu, kas notiek pārējos. Atgrieziet, lūdzu , galveno skatu ar visiem kontiem!</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Zanete9</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-25T09:32:22-07:00</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>11873774178</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id356476596</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Widget removed</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>Hate that you have removed widget for quickly checking account balance.</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Sezo1!</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-24T04:45:23-07:00</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>11869101241</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id421156522</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>Revolut bez revolūcijas</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>Google Tag Manager, Facebook SDK ir ieslēgtas pēc noklusējuma. Atrodas īsti neatrodamā vietā. Jūs esat banka vai vietne ar receptēm?
+Ar ikonām, kuras pārdeva kaut kādabetting platforma. Neapmierina, ka uz lielā telefona neietilpst bez ritināšanas: mani konti, mani maksājumi un iestatījumi.
+Kopsavilkums: šī ir lietotne pusakliem, bezgaumīgiem spēlmaņiem. Skumji 😢</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>vershart</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-23T12:50:14-07:00</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>11866920387</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id533968658</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>New app look🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>Amazing job done by development and design team! 🔥 app looks outstanding! Big thanks!🫶🏻</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Denchill21</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-23T08:32:33-07:00</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>11866172369</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1315685789</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Poor user experience</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>Outdated design and limited functionality of the app. Unclear transaction history with delayed transactions being shown out of sequence. Only the date of transaction is specified, but not the time. 3D secure is much more inconvenient to use, compared to SmartID. Please explore the interface of Chase UK and consider making improvements to Citadele banking app.</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>34 vsk</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>2024-09-30T05:34:19-07:00</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>11781257580</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id297713306</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>Citadele</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>Labākā banku aplikācija</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Sakals</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>14.2</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-25T07:24:11-07:00</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>11421615443</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id42359889</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Citadel</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>Iesaku! 🤩</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>azakin78</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-10T02:39:38-07:00</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>11251572473</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id797903164</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>Viss labi pārdomāts</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>Ērta, pārskatāma, viegli saprotama un izmantojama aplikācija. Ļoti patīk.</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Laumelle</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>2024-03-20T00:23:59-07:00</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>11064372679</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id907753487</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>Not version on iPad</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>I want version on iPad</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>rek1ngs</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>2024-03-05T10:31:05-07:00</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>11011804833</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1409702477</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>Love it</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>Palīdz parsutit naudu, sanemt naudu. iesaku visiem!</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>𝐄𝐥𝐥𝐚𓆉</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>2024-03-04T07:16:56-07:00</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>11007581975</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1234649714</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Best banking app ever</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>I really like this app:)</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>mlpplgip</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-24T08:45:02-07:00</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>10975091972</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1482507137</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>Quick balance not working</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>In last couple months, constant message showing “SSL error” on the widget. Very annoying.
+Last iOS and last app version.</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>dkrasilnikov87</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-22T21:28:50-07:00</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>10969502166</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1285648071</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>Quick balance not working</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>Quick balance widget stopped working for last two months showing SSL error. Before that it was updating the balance only after the app itself was opened, which made it barely useful</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>zeco2309</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-12T00:43:08-07:00</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>10929966350</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id101566404</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Ātrais atlikums lielākoties nestrādā</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>Jau vairāk kā mēnesi gaidu, kad tiks sakārtota opcija par ātro atlikumu un būs programmas atjauninājums. Šī problēma ir ļoti regulāra, priekš kam piedāvāt tādu opciju, ja vienmēr ir SSL error??? Vienmēr jāiet bankā, lai paskatītos atlikumu, taču nodrošiniet aplikācijas pilnveidīgu funkcionēšanu, šī ir bankas aplikācija nevis spēlītes… pati banka pilnīgi apmierina, bet mūžīgi ķibeles ar aplikāciju.</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>RozeeEl</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-09T10:49:38-07:00</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>10920582816</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id832314400</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>Widget is not working</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>Widget is not working on last ios version due to an SSL error</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>risasidl</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-06T09:42:29-07:00</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>10909249974</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id406941781</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>Widget is not working</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>I have instant SSL issue on the widget. Reinstall did not work.</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>alastarfox</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-05T04:36:45-07:00</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>10904428818</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id136066300</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>Widget error</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>The most useful funtion not working anymore.
+Latest iOS/device and Citadele app. 
+2 stars for good app with push notification. 3 more stars will be when widgets will work again</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>walkerS07</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-03T03:09:21-07:00</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>10896344614</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id141053556</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>Face id does not work</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>I'm constantly getting an error message when I'm trying to activate the Face Id</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>mortex231094</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-01T15:11:21-07:00</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>10890452120</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id553444918</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>widget error</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>Newest ios version but still doesn’t work widget, “SSL error” almost few months</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>bublik02</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-01T00:58:33-07:00</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>10887912242</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id651196055</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>App crash</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>„An SSL error has occured and a secure connection to the server cannot be made on iOS 14.8” Week ago everything worked fine</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>usdvgh</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>12.48</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>2024-01-12T22:41:55-07:00</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>10816064645</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1567530686</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>Nice one</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>Nice one</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>dmi3j</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>2023-12-20T04:48:56-07:00</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>10722314576</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id178776926</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Netieku aplikācijā!</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>ejot aplikācijā un spiežot pieslēgties izmet kļūdu ka ir problēma ar SSL, nevar droši pieslēgties. Visu dienu mēģinu jau tikt aplikācijā!! 
+Iepriekš problēmu nebija.</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Nickwitha</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>2023-12-19T03:34:48-07:00</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>10716910882</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1349178942</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>Tranzakcijas problēmas</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>Vienmēr kaut kadi tur darbi notiek  , tā nevar zibmaksājumu veikt , tā nevar Ienākt banka , vienmēr atradīsies kaut kāda problēma vai kļūda kura jums truces darboties , tāpēc laipni Lūgti Citadele un atsuksmes kur ir 5 star tas ir fake , lietoju jūsu banku tāpēc ka nav citas izvēles diemžēl  , paldies par labu servisu , aplikācija ir problemātikas katru reizi</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Janis 0zols</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>13.6</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>2023-12-09T03:36:35-07:00</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>10673996577</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1527333568</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>Mobile scan nestrādā</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>Nav iespējams nekādā veidā noskenēt kodu, ja tas ir telefona ekrānā. Mobile scan ir iespējams lietot tikai tad, ja maksājumi tiek veikti no datora. Ļoti neērti un bezjēdzīgi.</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>SJ9811</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-12T02:15:50-07:00</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>10360107536</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id584257643</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>Ikonas</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>Man patīn kad ir jaunas lietotnes ikonas</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Marta😫🙄🤬😝</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-02T22:04:48-07:00</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>10328645033</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1350016099</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>Ну косяк же</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>Когда после введения логина-пароля аппликация спрашивает код и переключаюсь на фото кодовой карты и обратно - нет возможности этот код ввести, виртуальная клавиатура больше не доступна. Тап что аппликацию использовать совершенно не возможно.</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Alex-7375</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>2023-05-24T02:21:43-07:00</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>9959835797</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id399118566</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>SSL kļūda</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>Pirms atvērt aplikāciju raksta SSL kļūda…nezinu vai tas ietekmē drošību atvērot..bet nav patīkami to redzēt.</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Lvdelfi</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>2023-05-05T09:39:38-07:00</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>9895755133</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id244766505</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>Melns ekrāns</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>Ļoti bieži izmantojot MobileScan atver lietotni un ir melns ekrāns, tad atkal par jaunu un tikai tad aiziet. Bieži arī vienkārši atverot aplikāciju ir tieši šī pati problēma, melns ekrāns un viss. Man ir Iphone 13 Pro Max, jaunākā Ios versija, aplikācija arī Citadele atjaunināta. Nekas nelīdz. Un šis jau ir vairākus mēnešus. Ļoti apgrūtina veikt maksājumus internetā!</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Badddaa</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>2023-04-01T13:34:09-07:00</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>9776448917</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id521495447</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>…овноприложение</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>После обновления , мобильное приложения перестало работать, при любой операции выдает ошибку,приложение снес с телефона, теперь не могу заинсталить заного, полный отстой</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Android444</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>2023-03-19T09:27:38-07:00</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>9730504104</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1174712803</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>Melns ekrāns</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>Aplikācija uzkarās, un katru reizi tā jādzēš ārā un jāinstalē no jauna. Tad notiek jau aptuveni gada griezumā. Vidēji 2-3 reizes mēnesī.</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>diaaaaassss</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>2023-03-14T05:09:08-07:00</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>9712186505</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id953526853</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>Melns ekrāns</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>Kārtējo reizi ir aplukācija jāpārinstalē, jo parādās melns ekrāns. Tas ir kaitinoši.</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Best suricata</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>12.48</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>2023-02-26T03:26:40-07:00</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>9657260669</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id326775101</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>Red scren bug</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>3 no 5 reizēm,kad mēģinu atvērt aplikāciju,parādās sarkans ekrāns un jāver vaļā pa jaunu. Gan vecajam,gan jaunajam telefonam.   Citiem paziņām ir tāda pati problēma. Tehniskais serviss ne visai pieklājīgi atbild,lai pārbaudu,vai man ir jaunākā versija. Bet pēc pārējām atsauksmēm ir skaidrs,ka daudziem ir šī problēma. 
+3x from 5 when opening app,there is just red screen. On old and new phone the same. Also other friends have the same bug. When writing to tehnical help,they are not very polite and just answers that i need to check if i have newest version. But from other reviews it's clear that many users have similar problems.</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>evijavarta</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>12.48</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>2023-02-19T07:32:29-07:00</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>9634102041</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id596817186</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>Mobila aplikacija nestrada</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>Reti, kad mobila aplikacija ir lietojama. Jau kadu menesi bija melns ekrans, tagad sarkans ekrans. Cik reizes jau neesmu izdzesusi aplikaciju, un atpakal instaleju. zel!!</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>ievarinalds</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>12.48</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>2023-02-14T00:05:40-07:00</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>9616068166</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id641470460</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>Problems using MobileScan</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>When trying to authenticate a purchase on the phone, app won’t open or give a notification about MobileScan authorisation.</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>temporaryec</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>12.47</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>2022-12-12T21:01:59-07:00</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>9390560788</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1467648957</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>Salabojiet bugs!!!</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>Katru nedēļu jāinstalē app no jauna… atvērot app - melns vai sarkans ekrāns… palīdz tikai ja nodzēš un ielādē app no jauna.</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Ingridadem</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>12.47</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>2022-12-09T07:54:34-07:00</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>9377831093</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id199565521</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>Nekas pilnvērtīgi nestrādā!</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>Ātrais atlikums-neiet
+Paziņojumi-nenāk
+Atcerēties mani, saglabāt-neiet
+Pie ievadiet MobileSCAN PIN- kļūda! Kaut kas nogāja greizi. Pameiģiniet vel! 
+Vienu reizi jau pārinstalēju.</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Burlakss</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>12.47</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>2022-12-05T04:24:37-07:00</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>9363184138</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id538415840</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>terrible app</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>worst ever. Never co es up to IOS updates. If you want to live “off-line”, definetely choose this. Works out exactly in 50% cases</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>donna-078</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>12.47</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>2022-12-02T13:35:15-07:00</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>9353707439</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id930873476</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>Darbības problēmas</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>Nekas nemainās. Regulāri nevar apstiprināt maksājumus, atveras sarkans ekrāns un viss. Gadiem ilgas problēmas.</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Roliits</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>12.47</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>2022-10-23T13:05:24-07:00</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>9215050290</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id320430517</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>Citadele</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>Neiesaku lietot šo banku mani neapmierināja</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Den4ik20188</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>12.46</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>2022-08-27T05:18:13-07:00</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>9022708714</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id704507383</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>Citadele pielikums</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>Nestrādā! Regulāri pazūd! 😡</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Mmmmmmbvvvvvhhhhh</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>12.46</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>2022-08-25T10:51:50-07:00</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>9016127981</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1441355744</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>Kļūdas</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>Regulāri nestradā maksājumi,īpaši no Tele2 un Enefit rēķiniem pa tiešo nevar veikt apmaksu</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Janusex44</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>12.46</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>2022-07-08T21:36:14-07:00</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>8855345987</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id156306618</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>Login issues</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>After the latest update crashes 1 per 3 attempts to login</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>pinkfreudmd</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>12.45</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>2022-06-08T03:25:54-07:00</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>8753056750</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id963385833</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>Blank screen</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>When I open app only 1 from 5 times app works normal, in other time i see only blank screen. And I should delete and re-install app one more time.</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Olga_22052022</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>12.45</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>2022-05-22T01:12:47-07:00</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>8696042765</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1410921302</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>Nice app</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>Please fix issue that app sometimes quits after 1 second</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>ЙAARD</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>12.45</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>2022-05-20T05:21:10-07:00</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>8689679733</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id147247978</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>The Widget</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>This is a great banking app, there is no doubt in that, but when I open the app through the widget, it sometimes doesn’t authorise.</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Lion_Lv</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>12.45</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>2022-05-08T07:02:11-07:00</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>8650131507</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id794679289</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>Black screen</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>While paying with face ID sometimes just opens balck screen and its imposible to continue.</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>EndijsO</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>12.45</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>2022-05-06T21:21:01-07:00</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>8645114542</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id944347544</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>Black screen</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>It is a great App. Except one issue. Often when I try to open App I see just black screen. It is annoying.</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>OleksandrKo</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>12.45</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>2022-05-02T01:39:05-07:00</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>8628613993</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1398622639</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>Bugged</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>Bugged. The app does nothing when second pin code is entered.  No way to login with MobileScan.</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Galliec</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>12.45</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>2022-04-27T02:18:59-07:00</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>8610893337</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id340678224</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>Works very bad.</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>In comparison with orher banking apps this one is so so behind in development. A new card was delivered, I went to activate it and now it’s not displayed at all. I have to go to support for help? Also never shows fast balance.</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>nowaaay333</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>12.45</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>2022-04-26T14:38:39-07:00</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>8609414521</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id289628282</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>Иногда вылетает</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>Иногда при входе в приложение появляется ошибка, из-за чего приложение вылетает. В остальном же приложение очень даже хорошо сделано</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Horowary</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>12.44</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>2022-03-21T10:33:51-07:00</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>8480509212</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1390982561</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>Par daudz kļūdu</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>Pirms update nebija problēmu, viss apmierināja. 
+Pēc update mani met ārā no aplikācijas, kad vēlos veikt maksājumu. Pin kodu jāievada 3x lai aplikacija saprastu ka tas ir īstais, jo visu laiku met kļūdu. Nu nevar bankai būt tāda aplikācija. Tai jābūt uzticamai, bet šobrīd tā tieši izskatās pēc krāpnieku versijas ar ļoti daudz aizdomīgiem gļukiem.</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Anunamatata</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>12.44</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>2022-03-17T23:59:23-07:00</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>8467745651</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1075324188</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>TouchID</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>Почему больше нельзя войти в свой счет через TouchID. Требует постоянно логин и пароль входа. Раньше все работало.</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>ваадька</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>12.44</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>2022-03-03T02:58:23-07:00</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>8415391591</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1066182224</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>Can’t get in my bank.</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Nohlahgus</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>12.44</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>2022-02-26T07:41:07-07:00</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>8398694228</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id917242110</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>Пинкод</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>Не дает создать пинкод- пишет ошибку после повторения кода.</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Andrey Frost</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>12.44</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>2022-02-21T00:00:42-07:00</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>8379726719</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id586534715</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>🥸</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>Face ID isn’t working and mobile scan isn’t working as well🥲</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>imvsmodel</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>12.44</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>2022-02-20T14:57:32-07:00</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>8378503862</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1242888200</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>Logo</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>New logo is terribly ugly.. return the previous one please</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>jsjbtvjdjb</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>12.44</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>2022-02-19T01:54:18-07:00</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>8372340601</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id760296555</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>Hi. Since last update the app constantly asks for auth information like username. The checkbox "Saglabāt" ain't working.</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Sergejs.St</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>12.43</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>2021-12-21T03:33:35-07:00</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>8153201776</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1215224596</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>Regulāri nobrūk aplikācija un Mobile scan.</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>Miskaste ne aplikācija! Regulāri nobrūk Mobile scan, karās maksājumu saite uz aplikācijas apstiprināšanu. Ļoti slikts klientu serviss.</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Jeekabsons</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>12.43</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>2021-12-05T01:03:42-07:00</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>8097068557</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id391428258</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>Kļūda novērsta</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>Beidzot aplikācija strādā, tikai nepieciešams nevis apdeitot aplikāciju, bet gan izdzēst un tad reģistrēties. Tikai apdeitojot aplikāciju nav iespējams reģistrēties, joprojām parādās kļūdas paziņojums.</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>White House ghost</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>12.43</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>2021-12-03T02:45:09-07:00</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>8089879447</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id276215849</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>Kļūda</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>Uz iphone 13 ios 15.1 nevar izveidot paroli, izmetās kļūda.</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Maucenaiks</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>12.41</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>2021-10-28T10:04:31-07:00</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>7963332877</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id86935130</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>Сплошное расстройство</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>MobileScan в двадцать восемнадцатый раз «забывает» меня и вынуждает переться в банк, чтобы восстановить доступ к счетам с нужными лимитами. Редкостный говноexperience. Никакие чудо-кредитки, херо карты, и х реворды не спасают. Ухожу из банка.</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Mihails.Galuska</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>12.41</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>2021-10-19T12:32:20-07:00</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>7932287047</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id108465413</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>Aplikācija neatbild, nekādas reakcijas no tehniskā atbalsta.</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>Jaunākā aplikācijas versija ar iOS 14.7.1 nestrādā. Rāda nepareizu paroli. Izdodas ielogoties tikai pēc paroles maiņas. Nākošo reizi atkal rāda nepareizu paroli. Atbalsts ieteica pārinstalēt aplikāciju (taot nestrādā). Tālāku atbalstu neviens nesniedz. Es nespēju tikt pie saviem līdzekļiem un banka IGNORĒ un pat netaisās neko darīt?</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>katyyy1111</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>12.41</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>2021-10-17T09:14:36-07:00</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>7925130489</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1339911016</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>FaceID is not working anymore</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>Needed option is enabled. Tried to toggle few times, but no luck</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>anton.wise</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>12.35</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>2021-02-28T21:54:40-07:00</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>7051530499</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id942397956</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K48"/>
+  <autoFilter ref="A1:K148"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3204,7 +8521,7 @@
         <v/>
       </c>
       <c r="C5" s="7">
-        <f>IFERROR(AVERAGE(Reviews!C2:C48),0)</f>
+        <f>IFERROR(AVERAGE(Reviews!C2:C148),0)</f>
         <v/>
       </c>
       <c r="D5" s="6">
